--- a/movilizacion/entregables/Simulador_Movilizacion_GRS110.xlsx
+++ b/movilizacion/entregables/Simulador_Movilizacion_GRS110.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1649" uniqueCount="848">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1649" uniqueCount="849">
   <si>
     <t xml:space="preserve">Simulador de movilización del taladro GRS 110 · La Cira Infantas</t>
   </si>
@@ -120,7 +120,7 @@
     <t xml:space="preserve">Lista: las 3 ofertas (Lump Sum con y sin descuento)</t>
   </si>
   <si>
-    <t xml:space="preserve">Bono del Work Order por mover más rápido (% sobre la tarifa) · tabla WO por horas pendiente</t>
+    <t xml:space="preserve">Ajuste a la tarifa WO (%) · las del Excel son el TOPE (movilización rápida); si tarda más paga una tarifa fija menor: solo 0 o negativo</t>
   </si>
   <si>
     <t xml:space="preserve">Adicionales sobre tarifa base (Petro Star normal y Ecotransur)</t>
@@ -693,16 +693,16 @@
     <t xml:space="preserve">No es monótona: 5–10 km (95.374) cuesta menos que 0,1–5 km (98.663).</t>
   </si>
   <si>
-    <t xml:space="preserve">Bono por mover más rápido</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Escalón por banda de horas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bandas de horas de la tabla WO (pendiente)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Las tarifas del Excel son 'más de X horas' (banda lenta). Mover más rápido sube la tarifa del WO: el WO puede costar más que en el caso base.</t>
+    <t xml:space="preserve">Tarifa con tope</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acotada arriba y abajo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tope superior = tarifa del Excel (movilización rápida); si tarda más, tarifa fija menor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El WO nunca paga más que la tarifa del Excel, tarde lo que tarde. Comparar contra el tope es el escenario más caro del WO, es decir, el más favorable al tercerizado.</t>
   </si>
   <si>
     <t xml:space="preserve">Variable; escalón 1 o 2 turnos</t>
@@ -1884,399 +1884,402 @@
     <t xml:space="preserve">Su carta no declara tiempos ni tarifas horarias.</t>
   </si>
   <si>
-    <t xml:space="preserve">Bono del WO por mover más rápido = 0 %</t>
+    <t xml:space="preserve">WO a su tarifa tope en todas las movilizaciones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Es el WO más caro posible: favorece al tercerizado. Si alguna tarda más, el WO paga menos.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meses bloqueados = 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Riesgo operativo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cada mes bloqueado paga el cargo fijo de 0 movilizaciones.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bloqueo social/escolar en movilización: 17,3 h por campaña, pagadas con taladro + equipos (condición 7); el WO no paga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medido (OpenWells 2025) escalado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22,25 h en 45 movs de 2025 → 35/45. Si el contrato WO cobrara stand-by por bloqueos, el efecto se cancela en parte.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lump Sum sin descuento (principal)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Con descuento: solo referencia.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ecotransur 6ª+ en misma loc. = equipos 0–5 km</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El PDF no trae valor.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Orden de los pozos dentro del mes: intercalado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sensibilidad: misma loc. primero / otra primero.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Horas pagadas al taladro = horas del Excel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los logs muestran más horas en misma loc. y 0,1–5 km (2025).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NPT de perforación 0 %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barrido 0–20 % en Sensibilidad.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fin de campaña = fin del contrato (no se cobra)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solo los bloqueos con contrato vigente pagan cargo fijo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Más de 20 km se paga con la tarifa de 10–20 km</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 movimiento en 2024.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IVA fuera del análisis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sensibilidad: de qué depende que haya o no ahorro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ahorro = costo WO − costo tercerizado (USD); positivo = el tercerizado cuesta menos. Campaña 15 misma loc. + 20 en 0,1–5 km, TRM 3.700, 17,3 h de bloqueo social en movilización (OpenWells 2025). Valores calculados con tools/sensibilidad.py (mismo motor que el simulador); no se recalculan al editar.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. FRECUENCIA: AHORRO DE LA CAMPAÑA SEGÚN MOVILIZACIONES POR MES (esperado 5–6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Movs/mes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PS normal · horas Excel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lump Sum · horas Excel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ecotransur · horas Excel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PS normal · horas cotizadas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lump Sum · horas cotizadas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ecotransur · horas cotizadas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4,5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5,5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6,5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Horas cotizadas = 12/24/36/36 h (Cot. 1255). Con frecuencias no enteras se alternan meses (p. ej. 5,5 = meses de 6 y de 5). El último mes de la campaña puede quedar corto y pagar cargo fijo: por eso la curva tiene dientes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. PUNTOS DE QUIEBRE: CUÁNTO AGUANTA EL AHORRO ANTES DE DESAPARECER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oferta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ahorro campaña (USD)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">% del costo de un pozo (550 k)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Horas extra de taladro por movilización que lo anulan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Horas sobre el tiempo estipulado que lo anulan (taladro + equipos)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Días de taladro de demora en toda la campaña que lo anulan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meses bloqueados que lo anulan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Horas de bloqueo en movilización que lo anulan (campaña)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petro Star normal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hora excedida en el tercerizado: taladro 1.456 + equipos y señalizadores 1.357 = 2.813 USD/h (Cot. 1255 p. 5). En el Work Order cuesta 0. Un mes bloqueado: Petro Star 160.751 · Ecotransur 226.318 USD.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. LO QUE PASÓ CON LAS HORAS REALES (logs): campañas 2024 y 2025 repetidas con cada modelo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Año</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ahorro con horas Excel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ahorro con horas reales (solo taladro)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ahorro con horas reales + equipos por hora excedida</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Movilizaciones que exceden el tiempo estipulado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Horas excedidas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Equipos y señalizadores (USD)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taladro en esas horas (USD)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lump Sum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Horas reales: el taladro se paga por las horas reales (más o menos que el Excel). Las horas por encima de 12/24/36/36 h se cobran además en equipos y señalizadores (Cot. 1255 p. 5; Ecotransur con las mismas tarifas, supuesto).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4. TORNADO · Petro Star tarifa normal · 5 movs/mes · ahorro base 151.087 USD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valor base</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extremo que mejora</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ahorro (USD)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extremo que empeora</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Efecto (USD)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Premisa (5–6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5/mes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6/mes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Horas por encima del tiempo estipulado (taladro + equipos)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medido (logs)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 h</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+2 h sobre 12/24/36/36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cargo fijo de Petro Star con 5 movs/mes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medido (contradicción PDF)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">se cobra (p. 4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no se cobra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">se cobra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sobretiempo en cada movilización (solo taladro)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+3,5 h</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NPT de perforación (baja la frecuencia)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sin dato: barrido</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20 %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Horas de taladro por movilización</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dato Excel vs cotización</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Excel 12/18/24/28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petro Star 12/24/36/36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.944 USD/día</t>
+  </si>
+  <si>
+    <t xml:space="preserve">−10 %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+10 %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meses bloqueados (contrato vigente)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 mes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tarifa WO en movilizaciones lentas (bajo el tope)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Premisa SierraCol (tope)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tope</t>
+  </si>
+  <si>
+    <t xml:space="preserve">−5 % al WO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bloqueo social/escolar durante movilizaciones (h por campaña)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medido (OpenWells 2025)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3 h</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.6 h (el doble)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adicionales: ¿se cancelan entre modelos?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 % / 0 %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">se cancelan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+5 % solo en tercerizado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recargo de señalizadoras al WO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">se carga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no se carga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">por movilización</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60 M COP fijo por mes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4. TORNADO · Petro Star Lump Sum (sin descuento) · 5 movs/mes · ahorro base -453.862 USD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4. TORNADO · Ecotransur · 5 movs/mes · ahorro base 509.454 USD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4. TORNADO · Petro Star tarifa normal · 6 movs/mes · ahorro base 524.279 USD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Orden de los pozos dentro del mes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">intercalado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">misma loc. primero</t>
+  </si>
+  <si>
+    <t xml:space="preserve">otra loc. primero</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4. TORNADO · Petro Star Lump Sum (sin descuento) · 6 movs/mes · ahorro base -208.146 USD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4. TORNADO · Ecotransur · 6 movs/mes · ahorro base 587.204 USD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ecotransur 6ª+ en misma localización</t>
+  </si>
+  <si>
+    <t xml:space="preserve">equipos 0–5 km</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tarifa plena</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pendientes por confirmar: valor de trabajo y lo que está en juego</t>
+  </si>
+  <si>
+    <t xml:space="preserve">En juego = cambio del ahorro del tercerizado (USD) si el valor de trabajo cambia por la alternativa. Negativo = el tercerizado pierde ventaja. Campaña 15 + 20 en 0,1–5 km; columnas con 5 y 6 movs/mes. Valores fijos de tools/sensibilidad.py.</t>
   </si>
   <si>
     <t xml:space="preserve">Pendiente</t>
   </si>
   <si>
-    <t xml:space="preserve">Falta la tabla del WO por horas.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Meses bloqueados = 0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Riesgo operativo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cada mes bloqueado paga el cargo fijo de 0 movilizaciones.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bloqueo social/escolar en movilización: 17,3 h por campaña, pagadas con taladro + equipos (condición 7); el WO no paga</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Medido (OpenWells 2025) escalado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22,25 h en 45 movs de 2025 → 35/45. Si el contrato WO cobrara stand-by por bloqueos, el efecto se cancela en parte.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lump Sum sin descuento (principal)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Con descuento: solo referencia.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ecotransur 6ª+ en misma loc. = equipos 0–5 km</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El PDF no trae valor.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Orden de los pozos dentro del mes: intercalado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sensibilidad: misma loc. primero / otra primero.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Horas pagadas al taladro = horas del Excel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Los logs muestran más horas en misma loc. y 0,1–5 km (2025).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NPT de perforación 0 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Barrido 0–20 % en Sensibilidad.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fin de campaña = fin del contrato (no se cobra)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Solo los bloqueos con contrato vigente pagan cargo fijo.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Más de 20 km se paga con la tarifa de 10–20 km</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 movimiento en 2024.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IVA fuera del análisis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sensibilidad: de qué depende que haya o no ahorro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ahorro = costo WO − costo tercerizado (USD); positivo = el tercerizado cuesta menos. Campaña 15 misma loc. + 20 en 0,1–5 km, TRM 3.700, 17,3 h de bloqueo social en movilización (OpenWells 2025). Valores calculados con tools/sensibilidad.py (mismo motor que el simulador); no se recalculan al editar.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. FRECUENCIA: AHORRO DE LA CAMPAÑA SEGÚN MOVILIZACIONES POR MES (esperado 5–6)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Movs/mes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PS normal · horas Excel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lump Sum · horas Excel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ecotransur · horas Excel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PS normal · horas cotizadas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lump Sum · horas cotizadas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ecotransur · horas cotizadas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4,5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5,5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6,5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Horas cotizadas = 12/24/36/36 h (Cot. 1255). Con frecuencias no enteras se alternan meses (p. ej. 5,5 = meses de 6 y de 5). El último mes de la campaña puede quedar corto y pagar cargo fijo: por eso la curva tiene dientes.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2. PUNTOS DE QUIEBRE: CUÁNTO AGUANTA EL AHORRO ANTES DE DESAPARECER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oferta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ahorro campaña (USD)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">% del costo de un pozo (550 k)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Horas extra de taladro por movilización que lo anulan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Horas sobre el tiempo estipulado que lo anulan (taladro + equipos)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Días de taladro de demora en toda la campaña que lo anulan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Meses bloqueados que lo anulan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Horas de bloqueo en movilización que lo anulan (campaña)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petro Star normal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hora excedida en el tercerizado: taladro 1.456 + equipos y señalizadores 1.357 = 2.813 USD/h (Cot. 1255 p. 5). En el Work Order cuesta 0. Un mes bloqueado: Petro Star 160.751 · Ecotransur 226.318 USD.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3. LO QUE PASÓ CON LAS HORAS REALES (logs): campañas 2024 y 2025 repetidas con cada modelo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Año</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ahorro con horas Excel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ahorro con horas reales (solo taladro)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ahorro con horas reales + equipos por hora excedida</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Movilizaciones que exceden el tiempo estipulado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Horas excedidas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Equipos y señalizadores (USD)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taladro en esas horas (USD)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lump Sum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Horas reales: el taladro se paga por las horas reales (más o menos que el Excel). Las horas por encima de 12/24/36/36 h se cobran además en equipos y señalizadores (Cot. 1255 p. 5; Ecotransur con las mismas tarifas, supuesto).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4. TORNADO · Petro Star tarifa normal · 5 movs/mes · ahorro base 151.087 USD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valor base</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extremo que mejora</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ahorro (USD)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extremo que empeora</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Efecto (USD)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Premisa (5–6)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5/mes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6/mes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Horas por encima del tiempo estipulado (taladro + equipos)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Medido (logs)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 h</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+2 h sobre 12/24/36/36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cargo fijo de Petro Star con 5 movs/mes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Medido (contradicción PDF)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">se cobra (p. 4)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no se cobra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">se cobra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sobretiempo en cada movilización (solo taladro)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+3,5 h</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NPT de perforación (baja la frecuencia)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sin dato: barrido</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Horas de taladro por movilización</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dato Excel vs cotización</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Excel 12/18/24/28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petro Star 12/24/36/36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.944 USD/día</t>
-  </si>
-  <si>
-    <t xml:space="preserve">−10 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+10 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Meses bloqueados (contrato vigente)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 mes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bono del Work Order por mover más rápido</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pendiente (tabla WO)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+5 % al WO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bloqueo social/escolar durante movilizaciones (h por campaña)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Medido (OpenWells 2025)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3 h</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6 h (el doble)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adicionales: ¿se cancelan entre modelos?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 % / 0 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">se cancelan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+5 % solo en tercerizado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recargo de señalizadoras al WO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">se carga</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no se carga</t>
-  </si>
-  <si>
-    <t xml:space="preserve">por movilización</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60 M COP fijo por mes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4. TORNADO · Petro Star Lump Sum (sin descuento) · 5 movs/mes · ahorro base -453.862 USD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4. TORNADO · Ecotransur · 5 movs/mes · ahorro base 509.454 USD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4. TORNADO · Petro Star tarifa normal · 6 movs/mes · ahorro base 524.279 USD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Orden de los pozos dentro del mes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">intercalado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">misma loc. primero</t>
-  </si>
-  <si>
-    <t xml:space="preserve">otra loc. primero</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4. TORNADO · Petro Star Lump Sum (sin descuento) · 6 movs/mes · ahorro base -208.146 USD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4. TORNADO · Ecotransur · 6 movs/mes · ahorro base 587.204 USD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ecotransur 6ª+ en misma localización</t>
-  </si>
-  <si>
-    <t xml:space="preserve">equipos 0–5 km</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tarifa plena</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pendientes por confirmar: valor de trabajo y lo que está en juego</t>
-  </si>
-  <si>
-    <t xml:space="preserve">En juego = cambio del ahorro del tercerizado (USD) si el valor de trabajo cambia por la alternativa. Negativo = el tercerizado pierde ventaja. Campaña 15 + 20 en 0,1–5 km; columnas con 5 y 6 movs/mes. Valores fijos de tools/sensibilidad.py.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Valor de trabajo</t>
   </si>
   <si>
@@ -2295,19 +2298,19 @@
     <t xml:space="preserve">Quién confirma</t>
   </si>
   <si>
-    <t xml:space="preserve">Tabla del Work Order por horas (bono por mover más rápido)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tarifa 'más de X horas' (la más baja)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tarifas de bandas más rápidas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Todas (favorece al tercerizado)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SierraCol (contrato WO). Valor mostrado: +5 % al WO</t>
+    <t xml:space="preserve">Tarifa WO cuando la movilización tarda más (tarifa fija menor que el tope)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tope del Excel en todas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tarifa fija menor en las lentas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Todas (favorece al WO)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SierraCol (contrato WO). Valor mostrado: −5 % al WO</t>
   </si>
   <si>
     <t xml:space="preserve">Horas que se pagan al taladro</t>
@@ -2568,10 +2571,10 @@
     <t xml:space="preserve">Si una movilización supera el tiempo estipulado (12/24/36/36 h), se paga el taladro por esas horas y además equipos de la flota mínima y señalizadores por hora (Cot. 1255 p. 5). Simulador filas 41, 68, 69 y panel 1b.</t>
   </si>
   <si>
-    <t xml:space="preserve">Bono del Work Order</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Las tarifas WO del Excel son los ítems 'más de X horas' (la banda más lenta). Si el contratista mueve más rápido, el WO paga una tarifa mayor (bono). Sin la tabla WO por horas se deja como % editable (Simulador N10) en 0.</t>
+    <t xml:space="preserve">Tope del Work Order</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confirmado por SierraCol: las tarifas WO del Excel son el tope (lo máximo que se paga, con movilización rápida). Si la movilización tarda más, se paga una tarifa fija menor. El tercerizado no tiene tope: cada hora extra se paga (taladro + equipos). Simulador N10 = 0 %.</t>
   </si>
 </sst>
 </file>
@@ -21767,114 +21770,114 @@
         <v>618</v>
       </c>
       <c r="C27" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D27" s="7" t="s">
         <v>619</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>620</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="7" t="s">
+        <v>620</v>
+      </c>
+      <c r="C28" s="7" t="s">
         <v>621</v>
       </c>
-      <c r="C28" s="7" t="s">
+      <c r="D28" s="7" t="s">
         <v>622</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>623</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="7" t="s">
+        <v>623</v>
+      </c>
+      <c r="C29" s="7" t="s">
         <v>624</v>
       </c>
-      <c r="C29" s="7" t="s">
+      <c r="D29" s="7" t="s">
         <v>625</v>
-      </c>
-      <c r="D29" s="7" t="s">
-        <v>626</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="7" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="C30" s="7" t="s">
         <v>12</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="7" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="C31" s="7" t="s">
         <v>616</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="7" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="C32" s="7" t="s">
         <v>616</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B33" s="7" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="C33" s="7" t="s">
         <v>94</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="7" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="C34" s="7" t="s">
         <v>68</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B35" s="7" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="C35" s="7" t="s">
         <v>12</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B36" s="7" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="C36" s="7" t="s">
         <v>616</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B37" s="7" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="C37" s="7" t="s">
         <v>12</v>
@@ -21912,17 +21915,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="1" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="3" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
@@ -21934,30 +21937,30 @@
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="25" t="s">
+        <v>644</v>
+      </c>
+      <c r="C5" s="25" t="s">
         <v>645</v>
       </c>
-      <c r="C5" s="25" t="s">
+      <c r="D5" s="25" t="s">
         <v>646</v>
       </c>
-      <c r="D5" s="25" t="s">
+      <c r="E5" s="25" t="s">
         <v>647</v>
       </c>
-      <c r="E5" s="25" t="s">
+      <c r="F5" s="25" t="s">
         <v>648</v>
       </c>
-      <c r="F5" s="25" t="s">
+      <c r="G5" s="25" t="s">
         <v>649</v>
       </c>
-      <c r="G5" s="25" t="s">
+      <c r="H5" s="25" t="s">
         <v>650</v>
-      </c>
-      <c r="H5" s="25" t="s">
-        <v>651</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="7" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C6" s="49" t="n">
         <v>-83725.5391891883</v>
@@ -21980,7 +21983,7 @@
     </row>
     <row r="7" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="7" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C7" s="49" t="n">
         <v>32570.322162163</v>
@@ -22003,7 +22006,7 @@
     </row>
     <row r="8" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="7" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="C8" s="49" t="n">
         <v>151086.610270271</v>
@@ -22026,7 +22029,7 @@
     </row>
     <row r="9" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="7" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C9" s="49" t="n">
         <v>298418.601756758</v>
@@ -22049,7 +22052,7 @@
     </row>
     <row r="10" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="7" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="C10" s="49" t="n">
         <v>524278.884054055</v>
@@ -22072,7 +22075,7 @@
     </row>
     <row r="11" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="7" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="C11" s="49" t="n">
         <v>544289.827702703</v>
@@ -22095,7 +22098,7 @@
     </row>
     <row r="12" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="7" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="C12" s="49" t="n">
         <v>681834.461486487</v>
@@ -22118,7 +22121,7 @@
     </row>
     <row r="13" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="7" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="C13" s="49" t="n">
         <v>682640.878648649</v>
@@ -22141,12 +22144,12 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="2" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="3" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
@@ -22159,34 +22162,34 @@
     </row>
     <row r="17" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="25" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="C17" s="25" t="s">
+        <v>661</v>
+      </c>
+      <c r="D17" s="25" t="s">
         <v>662</v>
-      </c>
-      <c r="D17" s="25" t="s">
-        <v>663</v>
       </c>
       <c r="E17" s="25" t="s">
         <v>163</v>
       </c>
       <c r="F17" s="25" t="s">
+        <v>663</v>
+      </c>
+      <c r="G17" s="25" t="s">
         <v>664</v>
       </c>
-      <c r="G17" s="25" t="s">
+      <c r="H17" s="25" t="s">
         <v>665</v>
       </c>
-      <c r="H17" s="25" t="s">
+      <c r="I17" s="25" t="s">
         <v>666</v>
       </c>
-      <c r="I17" s="25" t="s">
+      <c r="J17" s="25" t="s">
         <v>667</v>
       </c>
-      <c r="J17" s="25" t="s">
+      <c r="K17" s="25" t="s">
         <v>668</v>
-      </c>
-      <c r="K17" s="25" t="s">
-        <v>669</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22194,7 +22197,7 @@
         <v>5</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="D18" s="49" t="n">
         <v>151086.610270271</v>
@@ -22258,7 +22261,7 @@
         <v>6</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="D20" s="49" t="n">
         <v>524278.884054055</v>
@@ -22319,12 +22322,12 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="2" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="3" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="C24" s="3"/>
       <c r="D24" s="3"/>
@@ -22337,39 +22340,39 @@
     </row>
     <row r="25" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="25" t="s">
+        <v>672</v>
+      </c>
+      <c r="C25" s="25" t="s">
+        <v>661</v>
+      </c>
+      <c r="D25" s="25" t="s">
         <v>673</v>
       </c>
-      <c r="C25" s="25" t="s">
-        <v>662</v>
-      </c>
-      <c r="D25" s="25" t="s">
+      <c r="E25" s="25" t="s">
         <v>674</v>
       </c>
-      <c r="E25" s="25" t="s">
+      <c r="F25" s="25" t="s">
         <v>675</v>
       </c>
-      <c r="F25" s="25" t="s">
+      <c r="G25" s="25" t="s">
         <v>676</v>
       </c>
-      <c r="G25" s="25" t="s">
+      <c r="H25" s="25" t="s">
         <v>677</v>
       </c>
-      <c r="H25" s="25" t="s">
+      <c r="I25" s="25" t="s">
         <v>678</v>
       </c>
-      <c r="I25" s="25" t="s">
+      <c r="J25" s="25" t="s">
         <v>679</v>
-      </c>
-      <c r="J25" s="25" t="s">
-        <v>680</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="7" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="D26" s="49" t="n">
         <v>1034726.05635135</v>
@@ -22395,7 +22398,7 @@
     </row>
     <row r="27" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="7" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="C27" s="7" t="s">
         <v>168</v>
@@ -22424,10 +22427,10 @@
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="7" t="s">
+        <v>680</v>
+      </c>
+      <c r="C28" s="7" t="s">
         <v>681</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>682</v>
       </c>
       <c r="D28" s="49" t="n">
         <v>-1074449.28027027</v>
@@ -22453,10 +22456,10 @@
     </row>
     <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="7" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="D29" s="49" t="n">
         <v>185171.784324325</v>
@@ -22482,7 +22485,7 @@
     </row>
     <row r="30" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="7" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="C30" s="7" t="s">
         <v>168</v>
@@ -22511,10 +22514,10 @@
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="7" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="D31" s="49" t="n">
         <v>-1192685.63054054</v>
@@ -22540,12 +22543,12 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="2" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="3" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="C34" s="3"/>
       <c r="D34" s="3"/>
@@ -22563,22 +22566,22 @@
         <v>8</v>
       </c>
       <c r="D35" s="25" t="s">
+        <v>685</v>
+      </c>
+      <c r="E35" s="25" t="s">
         <v>686</v>
       </c>
-      <c r="E35" s="25" t="s">
+      <c r="F35" s="25" t="s">
         <v>687</v>
       </c>
-      <c r="F35" s="25" t="s">
+      <c r="G35" s="25" t="s">
         <v>688</v>
       </c>
-      <c r="G35" s="25" t="s">
+      <c r="H35" s="25" t="s">
+        <v>687</v>
+      </c>
+      <c r="I35" s="25" t="s">
         <v>689</v>
-      </c>
-      <c r="H35" s="25" t="s">
-        <v>688</v>
-      </c>
-      <c r="I35" s="25" t="s">
-        <v>690</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22586,19 +22589,19 @@
         <v>79</v>
       </c>
       <c r="C36" s="7" t="s">
+        <v>690</v>
+      </c>
+      <c r="D36" s="7" t="s">
         <v>691</v>
       </c>
-      <c r="D36" s="7" t="s">
+      <c r="E36" s="7" t="s">
         <v>692</v>
-      </c>
-      <c r="E36" s="7" t="s">
-        <v>693</v>
       </c>
       <c r="F36" s="49" t="n">
         <v>524278.884054055</v>
       </c>
       <c r="G36" s="7" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="H36" s="49" t="n">
         <v>151086.610270271</v>
@@ -22609,22 +22612,22 @@
     </row>
     <row r="37" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B37" s="7" t="s">
+        <v>693</v>
+      </c>
+      <c r="C37" s="7" t="s">
         <v>694</v>
       </c>
-      <c r="C37" s="7" t="s">
+      <c r="D37" s="7" t="s">
         <v>695</v>
       </c>
-      <c r="D37" s="7" t="s">
-        <v>696</v>
-      </c>
       <c r="E37" s="7" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="F37" s="49" t="n">
         <v>151086.610270271</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="H37" s="49" t="n">
         <v>-220554.741081079</v>
@@ -22635,22 +22638,22 @@
     </row>
     <row r="38" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="7" t="s">
+        <v>697</v>
+      </c>
+      <c r="C38" s="7" t="s">
         <v>698</v>
       </c>
-      <c r="C38" s="7" t="s">
+      <c r="D38" s="7" t="s">
         <v>699</v>
       </c>
-      <c r="D38" s="7" t="s">
+      <c r="E38" s="7" t="s">
         <v>700</v>
-      </c>
-      <c r="E38" s="7" t="s">
-        <v>701</v>
       </c>
       <c r="F38" s="49" t="n">
         <v>437754.377027028</v>
       </c>
       <c r="G38" s="7" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="H38" s="49" t="n">
         <v>151086.610270271</v>
@@ -22661,22 +22664,22 @@
     </row>
     <row r="39" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B39" s="7" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="C39" s="7" t="s">
+        <v>694</v>
+      </c>
+      <c r="D39" s="7" t="s">
         <v>695</v>
       </c>
-      <c r="D39" s="7" t="s">
-        <v>696</v>
-      </c>
       <c r="E39" s="7" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="F39" s="49" t="n">
         <v>151086.610270271</v>
       </c>
       <c r="G39" s="7" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="H39" s="49" t="n">
         <v>-98524.4032432414</v>
@@ -22687,22 +22690,22 @@
     </row>
     <row r="40" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B40" s="7" t="s">
+        <v>704</v>
+      </c>
+      <c r="C40" s="7" t="s">
         <v>705</v>
       </c>
-      <c r="C40" s="7" t="s">
+      <c r="D40" s="7" t="s">
         <v>706</v>
       </c>
-      <c r="D40" s="7" t="s">
-        <v>707</v>
-      </c>
       <c r="E40" s="7" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="F40" s="49" t="n">
         <v>151086.610270271</v>
       </c>
       <c r="G40" s="7" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="H40" s="49" t="n">
         <v>-83725.5391891883</v>
@@ -22713,22 +22716,22 @@
     </row>
     <row r="41" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B41" s="7" t="s">
+        <v>708</v>
+      </c>
+      <c r="C41" s="7" t="s">
         <v>709</v>
       </c>
-      <c r="C41" s="7" t="s">
+      <c r="D41" s="7" t="s">
         <v>710</v>
       </c>
-      <c r="D41" s="7" t="s">
-        <v>711</v>
-      </c>
       <c r="E41" s="7" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="F41" s="49" t="n">
         <v>151086.610270271</v>
       </c>
       <c r="G41" s="7" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="H41" s="49" t="n">
         <v>-23633.3897297289</v>
@@ -22745,16 +22748,16 @@
         <v>18</v>
       </c>
       <c r="D42" s="7" t="s">
+        <v>712</v>
+      </c>
+      <c r="E42" s="7" t="s">
         <v>713</v>
-      </c>
-      <c r="E42" s="7" t="s">
-        <v>714</v>
       </c>
       <c r="F42" s="49" t="n">
         <v>232229.490270271</v>
       </c>
       <c r="G42" s="7" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="H42" s="49" t="n">
         <v>69943.7302702721</v>
@@ -22765,22 +22768,22 @@
     </row>
     <row r="43" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B43" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>621</v>
+      </c>
+      <c r="D43" s="7" t="s">
         <v>716</v>
       </c>
-      <c r="C43" s="7" t="s">
-        <v>622</v>
-      </c>
-      <c r="D43" s="7" t="s">
-        <v>717</v>
-      </c>
       <c r="E43" s="7" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="F43" s="49" t="n">
         <v>151086.610270271</v>
       </c>
       <c r="G43" s="7" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="H43" s="49" t="n">
         <v>-9664.7410810804</v>
@@ -22791,28 +22794,28 @@
     </row>
     <row r="44" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B44" s="7" t="s">
+        <v>718</v>
+      </c>
+      <c r="C44" s="7" t="s">
         <v>719</v>
       </c>
-      <c r="C44" s="7" t="s">
+      <c r="D44" s="7" t="s">
         <v>720</v>
       </c>
-      <c r="D44" s="7" t="s">
-        <v>707</v>
-      </c>
       <c r="E44" s="7" t="s">
+        <v>720</v>
+      </c>
+      <c r="F44" s="49" t="n">
+        <v>151086.610270271</v>
+      </c>
+      <c r="G44" s="7" t="s">
         <v>721</v>
       </c>
-      <c r="F44" s="49" t="n">
-        <v>306481.11027027</v>
-      </c>
-      <c r="G44" s="7" t="s">
-        <v>707</v>
-      </c>
       <c r="H44" s="49" t="n">
-        <v>151086.610270271</v>
+        <v>-4307.88972973032</v>
       </c>
       <c r="I44" s="49" t="n">
-        <v>155394.499999999</v>
+        <v>155394.500000001</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22826,7 +22829,7 @@
         <v>724</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="F45" s="49" t="n">
         <v>199754.315675676</v>
@@ -22939,42 +22942,42 @@
         <v>8</v>
       </c>
       <c r="D51" s="25" t="s">
+        <v>685</v>
+      </c>
+      <c r="E51" s="25" t="s">
         <v>686</v>
       </c>
-      <c r="E51" s="25" t="s">
+      <c r="F51" s="25" t="s">
         <v>687</v>
       </c>
-      <c r="F51" s="25" t="s">
+      <c r="G51" s="25" t="s">
         <v>688</v>
       </c>
-      <c r="G51" s="25" t="s">
+      <c r="H51" s="25" t="s">
+        <v>687</v>
+      </c>
+      <c r="I51" s="25" t="s">
         <v>689</v>
-      </c>
-      <c r="H51" s="25" t="s">
-        <v>688</v>
-      </c>
-      <c r="I51" s="25" t="s">
-        <v>690</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B52" s="7" t="s">
+        <v>693</v>
+      </c>
+      <c r="C52" s="7" t="s">
         <v>694</v>
       </c>
-      <c r="C52" s="7" t="s">
+      <c r="D52" s="7" t="s">
         <v>695</v>
       </c>
-      <c r="D52" s="7" t="s">
-        <v>696</v>
-      </c>
       <c r="E52" s="7" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="F52" s="49" t="n">
         <v>-453861.708648649</v>
       </c>
       <c r="G52" s="7" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="H52" s="49" t="n">
         <v>-825503.059999999</v>
@@ -22985,22 +22988,22 @@
     </row>
     <row r="53" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B53" s="7" t="s">
+        <v>697</v>
+      </c>
+      <c r="C53" s="7" t="s">
         <v>698</v>
       </c>
-      <c r="C53" s="7" t="s">
+      <c r="D53" s="7" t="s">
         <v>699</v>
       </c>
-      <c r="D53" s="7" t="s">
+      <c r="E53" s="7" t="s">
         <v>700</v>
-      </c>
-      <c r="E53" s="7" t="s">
-        <v>701</v>
       </c>
       <c r="F53" s="49" t="n">
         <v>-167193.941891892</v>
       </c>
       <c r="G53" s="7" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="H53" s="49" t="n">
         <v>-453861.708648649</v>
@@ -23011,22 +23014,22 @@
     </row>
     <row r="54" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B54" s="7" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="C54" s="7" t="s">
+        <v>694</v>
+      </c>
+      <c r="D54" s="7" t="s">
         <v>695</v>
       </c>
-      <c r="D54" s="7" t="s">
-        <v>696</v>
-      </c>
       <c r="E54" s="7" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="F54" s="49" t="n">
         <v>-453861.708648649</v>
       </c>
       <c r="G54" s="7" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="H54" s="49" t="n">
         <v>-703472.722162161</v>
@@ -23040,19 +23043,19 @@
         <v>79</v>
       </c>
       <c r="C55" s="7" t="s">
+        <v>690</v>
+      </c>
+      <c r="D55" s="7" t="s">
         <v>691</v>
       </c>
-      <c r="D55" s="7" t="s">
+      <c r="E55" s="7" t="s">
         <v>692</v>
-      </c>
-      <c r="E55" s="7" t="s">
-        <v>693</v>
       </c>
       <c r="F55" s="49" t="n">
         <v>-208146.48</v>
       </c>
       <c r="G55" s="7" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="H55" s="49" t="n">
         <v>-453861.708648649</v>
@@ -23063,22 +23066,22 @@
     </row>
     <row r="56" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B56" s="7" t="s">
+        <v>704</v>
+      </c>
+      <c r="C56" s="7" t="s">
         <v>705</v>
       </c>
-      <c r="C56" s="7" t="s">
+      <c r="D56" s="7" t="s">
         <v>706</v>
       </c>
-      <c r="D56" s="7" t="s">
-        <v>707</v>
-      </c>
       <c r="E56" s="7" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="F56" s="49" t="n">
         <v>-453861.708648649</v>
       </c>
       <c r="G56" s="7" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="H56" s="49" t="n">
         <v>-688673.858108108</v>
@@ -23089,22 +23092,22 @@
     </row>
     <row r="57" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B57" s="7" t="s">
+        <v>708</v>
+      </c>
+      <c r="C57" s="7" t="s">
         <v>709</v>
       </c>
-      <c r="C57" s="7" t="s">
+      <c r="D57" s="7" t="s">
         <v>710</v>
       </c>
-      <c r="D57" s="7" t="s">
-        <v>711</v>
-      </c>
       <c r="E57" s="7" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="F57" s="49" t="n">
         <v>-453861.708648649</v>
       </c>
       <c r="G57" s="7" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="H57" s="49" t="n">
         <v>-628581.708648649</v>
@@ -23121,16 +23124,16 @@
         <v>18</v>
       </c>
       <c r="D58" s="7" t="s">
+        <v>712</v>
+      </c>
+      <c r="E58" s="7" t="s">
         <v>713</v>
-      </c>
-      <c r="E58" s="7" t="s">
-        <v>714</v>
       </c>
       <c r="F58" s="49" t="n">
         <v>-372718.828648648</v>
       </c>
       <c r="G58" s="7" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="H58" s="49" t="n">
         <v>-535004.588648646</v>
@@ -23141,22 +23144,22 @@
     </row>
     <row r="59" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B59" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="C59" s="7" t="s">
+        <v>621</v>
+      </c>
+      <c r="D59" s="7" t="s">
         <v>716</v>
       </c>
-      <c r="C59" s="7" t="s">
-        <v>622</v>
-      </c>
-      <c r="D59" s="7" t="s">
-        <v>717</v>
-      </c>
       <c r="E59" s="7" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="F59" s="49" t="n">
         <v>-453861.708648649</v>
       </c>
       <c r="G59" s="7" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="H59" s="49" t="n">
         <v>-614613.06</v>
@@ -23167,28 +23170,28 @@
     </row>
     <row r="60" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B60" s="7" t="s">
+        <v>718</v>
+      </c>
+      <c r="C60" s="7" t="s">
         <v>719</v>
       </c>
-      <c r="C60" s="7" t="s">
+      <c r="D60" s="7" t="s">
         <v>720</v>
       </c>
-      <c r="D60" s="7" t="s">
-        <v>707</v>
-      </c>
       <c r="E60" s="7" t="s">
+        <v>720</v>
+      </c>
+      <c r="F60" s="49" t="n">
+        <v>-453861.708648649</v>
+      </c>
+      <c r="G60" s="7" t="s">
         <v>721</v>
       </c>
-      <c r="F60" s="49" t="n">
-        <v>-298467.20864865</v>
-      </c>
-      <c r="G60" s="7" t="s">
-        <v>707</v>
-      </c>
       <c r="H60" s="49" t="n">
-        <v>-453861.708648649</v>
+        <v>-609256.20864865</v>
       </c>
       <c r="I60" s="49" t="n">
-        <v>155394.499999999</v>
+        <v>155394.500000001</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23228,7 +23231,7 @@
         <v>724</v>
       </c>
       <c r="E62" s="7" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="F62" s="49" t="n">
         <v>-405194.003243243</v>
@@ -23315,42 +23318,42 @@
         <v>8</v>
       </c>
       <c r="D67" s="25" t="s">
+        <v>685</v>
+      </c>
+      <c r="E67" s="25" t="s">
         <v>686</v>
       </c>
-      <c r="E67" s="25" t="s">
+      <c r="F67" s="25" t="s">
         <v>687</v>
       </c>
-      <c r="F67" s="25" t="s">
+      <c r="G67" s="25" t="s">
         <v>688</v>
       </c>
-      <c r="G67" s="25" t="s">
+      <c r="H67" s="25" t="s">
+        <v>687</v>
+      </c>
+      <c r="I67" s="25" t="s">
         <v>689</v>
-      </c>
-      <c r="H67" s="25" t="s">
-        <v>688</v>
-      </c>
-      <c r="I67" s="25" t="s">
-        <v>690</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B68" s="7" t="s">
+        <v>704</v>
+      </c>
+      <c r="C68" s="7" t="s">
         <v>705</v>
       </c>
-      <c r="C68" s="7" t="s">
+      <c r="D68" s="7" t="s">
         <v>706</v>
       </c>
-      <c r="D68" s="7" t="s">
-        <v>707</v>
-      </c>
       <c r="E68" s="7" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="F68" s="49" t="n">
         <v>509453.897297298</v>
       </c>
       <c r="G68" s="7" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="H68" s="49" t="n">
         <v>56818.851351351</v>
@@ -23361,22 +23364,22 @@
     </row>
     <row r="69" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B69" s="7" t="s">
+        <v>693</v>
+      </c>
+      <c r="C69" s="7" t="s">
         <v>694</v>
       </c>
-      <c r="C69" s="7" t="s">
+      <c r="D69" s="7" t="s">
         <v>695</v>
       </c>
-      <c r="D69" s="7" t="s">
-        <v>696</v>
-      </c>
       <c r="E69" s="7" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="F69" s="49" t="n">
         <v>509453.897297298</v>
       </c>
       <c r="G69" s="7" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="H69" s="49" t="n">
         <v>137812.545945949</v>
@@ -23387,22 +23390,22 @@
     </row>
     <row r="70" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B70" s="7" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="C70" s="7" t="s">
+        <v>694</v>
+      </c>
+      <c r="D70" s="7" t="s">
         <v>695</v>
       </c>
-      <c r="D70" s="7" t="s">
-        <v>696</v>
-      </c>
       <c r="E70" s="7" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="F70" s="49" t="n">
         <v>509453.897297298</v>
       </c>
       <c r="G70" s="7" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="H70" s="49" t="n">
         <v>259842.883783785</v>
@@ -23413,22 +23416,22 @@
     </row>
     <row r="71" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B71" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="C71" s="7" t="s">
+        <v>621</v>
+      </c>
+      <c r="D71" s="7" t="s">
         <v>716</v>
       </c>
-      <c r="C71" s="7" t="s">
-        <v>622</v>
-      </c>
-      <c r="D71" s="7" t="s">
-        <v>717</v>
-      </c>
       <c r="E71" s="7" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="F71" s="49" t="n">
         <v>509453.897297298</v>
       </c>
       <c r="G71" s="7" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="H71" s="49" t="n">
         <v>283136.374324325</v>
@@ -23439,22 +23442,22 @@
     </row>
     <row r="72" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B72" s="7" t="s">
+        <v>708</v>
+      </c>
+      <c r="C72" s="7" t="s">
         <v>709</v>
       </c>
-      <c r="C72" s="7" t="s">
+      <c r="D72" s="7" t="s">
         <v>710</v>
       </c>
-      <c r="D72" s="7" t="s">
-        <v>711</v>
-      </c>
       <c r="E72" s="7" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="F72" s="49" t="n">
         <v>509453.897297298</v>
       </c>
       <c r="G72" s="7" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="H72" s="49" t="n">
         <v>334733.897297299</v>
@@ -23471,16 +23474,16 @@
         <v>18</v>
       </c>
       <c r="D73" s="7" t="s">
+        <v>712</v>
+      </c>
+      <c r="E73" s="7" t="s">
         <v>713</v>
-      </c>
-      <c r="E73" s="7" t="s">
-        <v>714</v>
       </c>
       <c r="F73" s="49" t="n">
         <v>590596.777297298</v>
       </c>
       <c r="G73" s="7" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="H73" s="49" t="n">
         <v>428311.017297298</v>
@@ -23491,28 +23494,28 @@
     </row>
     <row r="74" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B74" s="7" t="s">
+        <v>718</v>
+      </c>
+      <c r="C74" s="7" t="s">
         <v>719</v>
       </c>
-      <c r="C74" s="7" t="s">
+      <c r="D74" s="7" t="s">
         <v>720</v>
       </c>
-      <c r="D74" s="7" t="s">
-        <v>707</v>
-      </c>
       <c r="E74" s="7" t="s">
+        <v>720</v>
+      </c>
+      <c r="F74" s="49" t="n">
+        <v>509453.897297298</v>
+      </c>
+      <c r="G74" s="7" t="s">
         <v>721</v>
       </c>
-      <c r="F74" s="49" t="n">
-        <v>664848.397297297</v>
-      </c>
-      <c r="G74" s="7" t="s">
-        <v>707</v>
-      </c>
       <c r="H74" s="49" t="n">
-        <v>509453.897297298</v>
+        <v>354059.397297297</v>
       </c>
       <c r="I74" s="49" t="n">
-        <v>155394.499999999</v>
+        <v>155394.500000001</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23526,7 +23529,7 @@
         <v>724</v>
       </c>
       <c r="E75" s="7" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="F75" s="49" t="n">
         <v>558121.602702703</v>
@@ -23572,19 +23575,19 @@
         <v>79</v>
       </c>
       <c r="C77" s="7" t="s">
+        <v>690</v>
+      </c>
+      <c r="D77" s="7" t="s">
         <v>691</v>
       </c>
-      <c r="D77" s="7" t="s">
+      <c r="E77" s="7" t="s">
         <v>692</v>
-      </c>
-      <c r="E77" s="7" t="s">
-        <v>693</v>
       </c>
       <c r="F77" s="49" t="n">
         <v>587203.900000001</v>
       </c>
       <c r="G77" s="7" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="H77" s="49" t="n">
         <v>509453.897297298</v>
@@ -23665,42 +23668,42 @@
         <v>8</v>
       </c>
       <c r="D82" s="25" t="s">
+        <v>685</v>
+      </c>
+      <c r="E82" s="25" t="s">
         <v>686</v>
       </c>
-      <c r="E82" s="25" t="s">
+      <c r="F82" s="25" t="s">
         <v>687</v>
       </c>
-      <c r="F82" s="25" t="s">
+      <c r="G82" s="25" t="s">
         <v>688</v>
       </c>
-      <c r="G82" s="25" t="s">
+      <c r="H82" s="25" t="s">
+        <v>687</v>
+      </c>
+      <c r="I82" s="25" t="s">
         <v>689</v>
-      </c>
-      <c r="H82" s="25" t="s">
-        <v>688</v>
-      </c>
-      <c r="I82" s="25" t="s">
-        <v>690</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B83" s="7" t="s">
+        <v>704</v>
+      </c>
+      <c r="C83" s="7" t="s">
         <v>705</v>
       </c>
-      <c r="C83" s="7" t="s">
+      <c r="D83" s="7" t="s">
         <v>706</v>
       </c>
-      <c r="D83" s="7" t="s">
-        <v>707</v>
-      </c>
       <c r="E83" s="7" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="F83" s="49" t="n">
         <v>524278.884054055</v>
       </c>
       <c r="G83" s="7" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="H83" s="49" t="n">
         <v>24921.921081082</v>
@@ -23714,19 +23717,19 @@
         <v>79</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="D84" s="7" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="E84" s="7" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="F84" s="49" t="n">
         <v>524278.884054055</v>
       </c>
       <c r="G84" s="7" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="H84" s="49" t="n">
         <v>151086.610270271</v>
@@ -23737,22 +23740,22 @@
     </row>
     <row r="85" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B85" s="7" t="s">
+        <v>693</v>
+      </c>
+      <c r="C85" s="7" t="s">
         <v>694</v>
       </c>
-      <c r="C85" s="7" t="s">
+      <c r="D85" s="7" t="s">
         <v>695</v>
       </c>
-      <c r="D85" s="7" t="s">
-        <v>696</v>
-      </c>
       <c r="E85" s="7" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="F85" s="49" t="n">
         <v>524278.884054055</v>
       </c>
       <c r="G85" s="7" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="H85" s="49" t="n">
         <v>152637.532702704</v>
@@ -23763,22 +23766,22 @@
     </row>
     <row r="86" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B86" s="7" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="C86" s="7" t="s">
+        <v>694</v>
+      </c>
+      <c r="D86" s="7" t="s">
         <v>695</v>
       </c>
-      <c r="D86" s="7" t="s">
-        <v>696</v>
-      </c>
       <c r="E86" s="7" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="F86" s="49" t="n">
         <v>524278.884054055</v>
       </c>
       <c r="G86" s="7" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="H86" s="49" t="n">
         <v>274667.870540542</v>
@@ -23789,22 +23792,22 @@
     </row>
     <row r="87" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B87" s="7" t="s">
+        <v>708</v>
+      </c>
+      <c r="C87" s="7" t="s">
         <v>709</v>
       </c>
-      <c r="C87" s="7" t="s">
+      <c r="D87" s="7" t="s">
         <v>710</v>
       </c>
-      <c r="D87" s="7" t="s">
-        <v>711</v>
-      </c>
       <c r="E87" s="7" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="F87" s="49" t="n">
         <v>524278.884054055</v>
       </c>
       <c r="G87" s="7" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="H87" s="49" t="n">
         <v>349558.884054055</v>
@@ -23821,16 +23824,16 @@
         <v>18</v>
       </c>
       <c r="D88" s="7" t="s">
+        <v>712</v>
+      </c>
+      <c r="E88" s="7" t="s">
         <v>713</v>
-      </c>
-      <c r="E88" s="7" t="s">
-        <v>714</v>
       </c>
       <c r="F88" s="49" t="n">
         <v>605421.764054055</v>
       </c>
       <c r="G88" s="7" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="H88" s="49" t="n">
         <v>443136.004054056</v>
@@ -23841,22 +23844,22 @@
     </row>
     <row r="89" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B89" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="C89" s="7" t="s">
+        <v>621</v>
+      </c>
+      <c r="D89" s="7" t="s">
         <v>716</v>
       </c>
-      <c r="C89" s="7" t="s">
-        <v>622</v>
-      </c>
-      <c r="D89" s="7" t="s">
-        <v>717</v>
-      </c>
       <c r="E89" s="7" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="F89" s="49" t="n">
         <v>524278.884054055</v>
       </c>
       <c r="G89" s="7" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="H89" s="49" t="n">
         <v>363527.532702703</v>
@@ -23867,28 +23870,28 @@
     </row>
     <row r="90" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B90" s="7" t="s">
+        <v>718</v>
+      </c>
+      <c r="C90" s="7" t="s">
         <v>719</v>
       </c>
-      <c r="C90" s="7" t="s">
+      <c r="D90" s="7" t="s">
         <v>720</v>
       </c>
-      <c r="D90" s="7" t="s">
-        <v>707</v>
-      </c>
       <c r="E90" s="7" t="s">
+        <v>720</v>
+      </c>
+      <c r="F90" s="49" t="n">
+        <v>524278.884054055</v>
+      </c>
+      <c r="G90" s="7" t="s">
         <v>721</v>
       </c>
-      <c r="F90" s="49" t="n">
-        <v>679673.384054054</v>
-      </c>
-      <c r="G90" s="7" t="s">
-        <v>707</v>
-      </c>
       <c r="H90" s="49" t="n">
-        <v>524278.884054055</v>
+        <v>368884.384054053</v>
       </c>
       <c r="I90" s="49" t="n">
-        <v>155394.499999999</v>
+        <v>155394.500000001</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23902,7 +23905,7 @@
         <v>724</v>
       </c>
       <c r="E91" s="7" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="F91" s="49" t="n">
         <v>572946.58945946</v>
@@ -23971,22 +23974,22 @@
     </row>
     <row r="94" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B94" s="7" t="s">
+        <v>697</v>
+      </c>
+      <c r="C94" s="7" t="s">
         <v>698</v>
       </c>
-      <c r="C94" s="7" t="s">
+      <c r="D94" s="7" t="s">
         <v>699</v>
       </c>
-      <c r="D94" s="7" t="s">
+      <c r="E94" s="7" t="s">
         <v>700</v>
-      </c>
-      <c r="E94" s="7" t="s">
-        <v>701</v>
       </c>
       <c r="F94" s="49" t="n">
         <v>565231.422162163</v>
       </c>
       <c r="G94" s="7" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="H94" s="49" t="n">
         <v>524278.884054055</v>
@@ -24067,42 +24070,42 @@
         <v>8</v>
       </c>
       <c r="D99" s="25" t="s">
+        <v>685</v>
+      </c>
+      <c r="E99" s="25" t="s">
         <v>686</v>
       </c>
-      <c r="E99" s="25" t="s">
+      <c r="F99" s="25" t="s">
         <v>687</v>
       </c>
-      <c r="F99" s="25" t="s">
+      <c r="G99" s="25" t="s">
         <v>688</v>
       </c>
-      <c r="G99" s="25" t="s">
+      <c r="H99" s="25" t="s">
+        <v>687</v>
+      </c>
+      <c r="I99" s="25" t="s">
         <v>689</v>
-      </c>
-      <c r="H99" s="25" t="s">
-        <v>688</v>
-      </c>
-      <c r="I99" s="25" t="s">
-        <v>690</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B100" s="7" t="s">
+        <v>704</v>
+      </c>
+      <c r="C100" s="7" t="s">
         <v>705</v>
       </c>
-      <c r="C100" s="7" t="s">
+      <c r="D100" s="7" t="s">
         <v>706</v>
       </c>
-      <c r="D100" s="7" t="s">
-        <v>707</v>
-      </c>
       <c r="E100" s="7" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="F100" s="49" t="n">
         <v>-208146.48</v>
       </c>
       <c r="G100" s="7" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="H100" s="49" t="n">
         <v>-580026.397837838</v>
@@ -24113,22 +24116,22 @@
     </row>
     <row r="101" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B101" s="7" t="s">
+        <v>693</v>
+      </c>
+      <c r="C101" s="7" t="s">
         <v>694</v>
       </c>
-      <c r="C101" s="7" t="s">
+      <c r="D101" s="7" t="s">
         <v>695</v>
       </c>
-      <c r="D101" s="7" t="s">
-        <v>696</v>
-      </c>
       <c r="E101" s="7" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="F101" s="49" t="n">
         <v>-208146.48</v>
       </c>
       <c r="G101" s="7" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="H101" s="49" t="n">
         <v>-579787.83135135</v>
@@ -24139,22 +24142,22 @@
     </row>
     <row r="102" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B102" s="7" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="C102" s="7" t="s">
+        <v>694</v>
+      </c>
+      <c r="D102" s="7" t="s">
         <v>695</v>
       </c>
-      <c r="D102" s="7" t="s">
-        <v>696</v>
-      </c>
       <c r="E102" s="7" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="F102" s="49" t="n">
         <v>-208146.48</v>
       </c>
       <c r="G102" s="7" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="H102" s="49" t="n">
         <v>-457757.493513512</v>
@@ -24168,19 +24171,19 @@
         <v>79</v>
       </c>
       <c r="C103" s="7" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="D103" s="7" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="E103" s="7" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="F103" s="49" t="n">
         <v>-208146.48</v>
       </c>
       <c r="G103" s="7" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="H103" s="49" t="n">
         <v>-453861.708648649</v>
@@ -24191,22 +24194,22 @@
     </row>
     <row r="104" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B104" s="7" t="s">
+        <v>708</v>
+      </c>
+      <c r="C104" s="7" t="s">
         <v>709</v>
       </c>
-      <c r="C104" s="7" t="s">
+      <c r="D104" s="7" t="s">
         <v>710</v>
       </c>
-      <c r="D104" s="7" t="s">
-        <v>711</v>
-      </c>
       <c r="E104" s="7" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="F104" s="49" t="n">
         <v>-208146.48</v>
       </c>
       <c r="G104" s="7" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="H104" s="49" t="n">
         <v>-382866.48</v>
@@ -24223,16 +24226,16 @@
         <v>18</v>
       </c>
       <c r="D105" s="7" t="s">
+        <v>712</v>
+      </c>
+      <c r="E105" s="7" t="s">
         <v>713</v>
-      </c>
-      <c r="E105" s="7" t="s">
-        <v>714</v>
       </c>
       <c r="F105" s="49" t="n">
         <v>-127003.599999999</v>
       </c>
       <c r="G105" s="7" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="H105" s="49" t="n">
         <v>-289289.359999998</v>
@@ -24243,22 +24246,22 @@
     </row>
     <row r="106" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B106" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="C106" s="7" t="s">
+        <v>621</v>
+      </c>
+      <c r="D106" s="7" t="s">
         <v>716</v>
       </c>
-      <c r="C106" s="7" t="s">
-        <v>622</v>
-      </c>
-      <c r="D106" s="7" t="s">
-        <v>717</v>
-      </c>
       <c r="E106" s="7" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="F106" s="49" t="n">
         <v>-208146.48</v>
       </c>
       <c r="G106" s="7" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="H106" s="49" t="n">
         <v>-368897.831351352</v>
@@ -24269,28 +24272,28 @@
     </row>
     <row r="107" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B107" s="7" t="s">
+        <v>718</v>
+      </c>
+      <c r="C107" s="7" t="s">
         <v>719</v>
       </c>
-      <c r="C107" s="7" t="s">
+      <c r="D107" s="7" t="s">
         <v>720</v>
       </c>
-      <c r="D107" s="7" t="s">
-        <v>707</v>
-      </c>
       <c r="E107" s="7" t="s">
+        <v>720</v>
+      </c>
+      <c r="F107" s="49" t="n">
+        <v>-208146.48</v>
+      </c>
+      <c r="G107" s="7" t="s">
         <v>721</v>
       </c>
-      <c r="F107" s="49" t="n">
-        <v>-52751.9800000009</v>
-      </c>
-      <c r="G107" s="7" t="s">
-        <v>707</v>
-      </c>
       <c r="H107" s="49" t="n">
-        <v>-208146.48</v>
+        <v>-363540.980000001</v>
       </c>
       <c r="I107" s="49" t="n">
-        <v>155394.499999999</v>
+        <v>155394.500000001</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -24330,7 +24333,7 @@
         <v>724</v>
       </c>
       <c r="E109" s="7" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="F109" s="49" t="n">
         <v>-159478.774594595</v>
@@ -24347,22 +24350,22 @@
     </row>
     <row r="110" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B110" s="7" t="s">
+        <v>697</v>
+      </c>
+      <c r="C110" s="7" t="s">
         <v>698</v>
       </c>
-      <c r="C110" s="7" t="s">
+      <c r="D110" s="7" t="s">
         <v>699</v>
       </c>
-      <c r="D110" s="7" t="s">
+      <c r="E110" s="7" t="s">
         <v>700</v>
-      </c>
-      <c r="E110" s="7" t="s">
-        <v>701</v>
       </c>
       <c r="F110" s="49" t="n">
         <v>-167193.941891892</v>
       </c>
       <c r="G110" s="7" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="H110" s="49" t="n">
         <v>-208146.48</v>
@@ -24443,42 +24446,42 @@
         <v>8</v>
       </c>
       <c r="D115" s="25" t="s">
+        <v>685</v>
+      </c>
+      <c r="E115" s="25" t="s">
         <v>686</v>
       </c>
-      <c r="E115" s="25" t="s">
+      <c r="F115" s="25" t="s">
         <v>687</v>
       </c>
-      <c r="F115" s="25" t="s">
+      <c r="G115" s="25" t="s">
         <v>688</v>
       </c>
-      <c r="G115" s="25" t="s">
+      <c r="H115" s="25" t="s">
+        <v>687</v>
+      </c>
+      <c r="I115" s="25" t="s">
         <v>689</v>
-      </c>
-      <c r="H115" s="25" t="s">
-        <v>688</v>
-      </c>
-      <c r="I115" s="25" t="s">
-        <v>690</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B116" s="7" t="s">
+        <v>693</v>
+      </c>
+      <c r="C116" s="7" t="s">
         <v>694</v>
       </c>
-      <c r="C116" s="7" t="s">
+      <c r="D116" s="7" t="s">
         <v>695</v>
       </c>
-      <c r="D116" s="7" t="s">
-        <v>696</v>
-      </c>
       <c r="E116" s="7" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="F116" s="49" t="n">
         <v>587203.900000001</v>
       </c>
       <c r="G116" s="7" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="H116" s="49" t="n">
         <v>215562.548648651</v>
@@ -24489,22 +24492,22 @@
     </row>
     <row r="117" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B117" s="7" t="s">
+        <v>704</v>
+      </c>
+      <c r="C117" s="7" t="s">
         <v>705</v>
       </c>
-      <c r="C117" s="7" t="s">
+      <c r="D117" s="7" t="s">
         <v>706</v>
       </c>
-      <c r="D117" s="7" t="s">
-        <v>707</v>
-      </c>
       <c r="E117" s="7" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="F117" s="49" t="n">
         <v>587203.900000001</v>
       </c>
       <c r="G117" s="7" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="H117" s="49" t="n">
         <v>283136.374324325</v>
@@ -24515,22 +24518,22 @@
     </row>
     <row r="118" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B118" s="7" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="C118" s="7" t="s">
+        <v>694</v>
+      </c>
+      <c r="D118" s="7" t="s">
         <v>695</v>
       </c>
-      <c r="D118" s="7" t="s">
-        <v>696</v>
-      </c>
       <c r="E118" s="7" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="F118" s="49" t="n">
         <v>587203.900000001</v>
       </c>
       <c r="G118" s="7" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="H118" s="49" t="n">
         <v>337592.886486488</v>
@@ -24541,22 +24544,22 @@
     </row>
     <row r="119" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B119" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="C119" s="7" t="s">
+        <v>621</v>
+      </c>
+      <c r="D119" s="7" t="s">
         <v>716</v>
       </c>
-      <c r="C119" s="7" t="s">
-        <v>622</v>
-      </c>
-      <c r="D119" s="7" t="s">
-        <v>717</v>
-      </c>
       <c r="E119" s="7" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="F119" s="49" t="n">
         <v>587203.900000001</v>
       </c>
       <c r="G119" s="7" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="H119" s="49" t="n">
         <v>360886.377027028</v>
@@ -24567,22 +24570,22 @@
     </row>
     <row r="120" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B120" s="7" t="s">
+        <v>708</v>
+      </c>
+      <c r="C120" s="7" t="s">
         <v>709</v>
       </c>
-      <c r="C120" s="7" t="s">
+      <c r="D120" s="7" t="s">
         <v>710</v>
       </c>
-      <c r="D120" s="7" t="s">
-        <v>711</v>
-      </c>
       <c r="E120" s="7" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="F120" s="49" t="n">
         <v>587203.900000001</v>
       </c>
       <c r="G120" s="7" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="H120" s="49" t="n">
         <v>412483.900000002</v>
@@ -24599,16 +24602,16 @@
         <v>18</v>
       </c>
       <c r="D121" s="7" t="s">
+        <v>712</v>
+      </c>
+      <c r="E121" s="7" t="s">
         <v>713</v>
-      </c>
-      <c r="E121" s="7" t="s">
-        <v>714</v>
       </c>
       <c r="F121" s="49" t="n">
         <v>668346.780000001</v>
       </c>
       <c r="G121" s="7" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="H121" s="49" t="n">
         <v>506061.020000001</v>
@@ -24619,28 +24622,28 @@
     </row>
     <row r="122" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B122" s="7" t="s">
+        <v>718</v>
+      </c>
+      <c r="C122" s="7" t="s">
         <v>719</v>
       </c>
-      <c r="C122" s="7" t="s">
+      <c r="D122" s="7" t="s">
         <v>720</v>
       </c>
-      <c r="D122" s="7" t="s">
-        <v>707</v>
-      </c>
       <c r="E122" s="7" t="s">
+        <v>720</v>
+      </c>
+      <c r="F122" s="49" t="n">
+        <v>587203.900000001</v>
+      </c>
+      <c r="G122" s="7" t="s">
         <v>721</v>
       </c>
-      <c r="F122" s="49" t="n">
-        <v>742598.4</v>
-      </c>
-      <c r="G122" s="7" t="s">
-        <v>707</v>
-      </c>
       <c r="H122" s="49" t="n">
-        <v>587203.900000001</v>
+        <v>431809.4</v>
       </c>
       <c r="I122" s="49" t="n">
-        <v>155394.499999999</v>
+        <v>155394.500000001</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -24654,7 +24657,7 @@
         <v>724</v>
       </c>
       <c r="E123" s="7" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="F123" s="49" t="n">
         <v>635871.605405407</v>
@@ -24726,19 +24729,19 @@
         <v>79</v>
       </c>
       <c r="C126" s="7" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="D126" s="7" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="E126" s="7" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="F126" s="49" t="n">
         <v>587203.900000001</v>
       </c>
       <c r="G126" s="7" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="H126" s="49" t="n">
         <v>509453.897297298</v>
@@ -24876,62 +24879,62 @@
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="25" t="s">
-        <v>619</v>
+        <v>749</v>
       </c>
       <c r="C4" s="25" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="D4" s="25" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="E4" s="25" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="F4" s="25" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="G4" s="25" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="H4" s="25" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="7" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="F5" s="49" t="n">
-        <v>155394.499999999</v>
+        <v>-155394.499999999</v>
       </c>
       <c r="G5" s="49" t="n">
-        <v>155394.499999999</v>
+        <v>-155394.499999999</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="7" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="C6" s="7" t="s">
+        <v>710</v>
+      </c>
+      <c r="D6" s="7" t="s">
         <v>711</v>
       </c>
-      <c r="D6" s="7" t="s">
-        <v>712</v>
-      </c>
       <c r="E6" s="7" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="F6" s="49" t="n">
         <v>-174720</v>
@@ -24940,21 +24943,21 @@
         <v>-174720</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="7" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="F7" s="49" t="n">
         <v>-160751.351351352</v>
@@ -24963,18 +24966,18 @@
         <v>-160751.351351352</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="7" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="E8" s="7" t="s">
         <v>168</v>
@@ -24986,21 +24989,21 @@
         <v>-226317.522972973</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="7" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="F9" s="49" t="n">
         <v>-2813.16216216216</v>
@@ -25009,21 +25012,21 @@
         <v>-2813.16216216216</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="7" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="C10" s="7" t="s">
+        <v>706</v>
+      </c>
+      <c r="D10" s="7" t="s">
         <v>707</v>
       </c>
-      <c r="D10" s="7" t="s">
-        <v>708</v>
-      </c>
       <c r="E10" s="7" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="F10" s="49" t="n">
         <v>-234812.149459459</v>
@@ -25032,18 +25035,18 @@
         <v>-499356.962972973</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="7" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="C11" s="7" t="s">
+        <v>706</v>
+      </c>
+      <c r="D11" s="7" t="s">
         <v>707</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>708</v>
       </c>
       <c r="E11" s="7" t="s">
         <v>168</v>
@@ -25055,21 +25058,21 @@
         <v>-304067.525675676</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="7" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>594</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="F12" s="49" t="n">
         <v>441153.14054054</v>
@@ -25078,21 +25081,21 @@
         <v>441153.14054054</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="7" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="F13" s="49" t="n">
         <v>0</v>
@@ -25101,21 +25104,21 @@
         <v>171565.113513514</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="7" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="F14" s="49" t="n">
         <v>286667.766756757</v>
@@ -25124,7 +25127,7 @@
         <v>40952.5381081081</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -25132,10 +25135,10 @@
         <v>744</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>168</v>
@@ -25152,10 +25155,10 @@
     </row>
     <row r="16" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="7" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>15</v>
@@ -25166,7 +25169,7 @@
       <c r="F16" s="49"/>
       <c r="G16" s="49"/>
       <c r="H16" s="7" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -25174,13 +25177,13 @@
         <v>248</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="D17" s="7" t="s">
         <v>734</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="F17" s="49" t="n">
         <v>-18918.9189189198</v>
@@ -25189,21 +25192,21 @@
         <v>-2702.70270270295</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="7" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="F18" s="49" t="n">
         <v>-88146.5310135125</v>
@@ -25212,7 +25215,7 @@
         <v>-81772.6787567558</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -25220,13 +25223,13 @@
         <v>730</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="F19" s="49" t="n">
         <v>-22297.2972972984</v>
@@ -25235,37 +25238,37 @@
         <v>-22297.2972972984</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="7" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="F20" s="49"/>
       <c r="G20" s="49"/>
       <c r="H20" s="7" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="7" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="E21" s="7" t="s">
         <v>168</v>
@@ -25273,26 +25276,26 @@
       <c r="F21" s="49"/>
       <c r="G21" s="49"/>
       <c r="H21" s="7" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="7" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="F22" s="49"/>
       <c r="G22" s="49"/>
       <c r="H22" s="7" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
     </row>
   </sheetData>
@@ -25325,38 +25328,38 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="1" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="25" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="C4" s="25" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="D4" s="25" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="E4" s="25" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="F4" s="25" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="G4" s="25" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="H4" s="25" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="I4" s="25" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="J4" s="25" t="s">
         <v>162</v>
@@ -25367,13 +25370,13 @@
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="7" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="E5" s="48" t="n">
         <v>37942.0110810811</v>
@@ -25391,21 +25394,21 @@
         <v>76047.4054054054</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="K5" s="7" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="7" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="E6" s="48" t="n">
         <v>48206.4554054054</v>
@@ -25423,21 +25426,21 @@
         <v>76047.4054054054</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="7" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>168</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="E7" s="48" t="n">
         <v>37900.8113513514</v>
@@ -25455,10 +25458,10 @@
         <v>76047.4054054054</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -25466,10 +25469,10 @@
         <v>90</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="E8" s="48" t="n">
         <v>59690.0227027027</v>
@@ -25487,10 +25490,10 @@
         <v>99473.8108108108</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -25498,10 +25501,10 @@
         <v>90</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="E9" s="48" t="n">
         <v>82239.1054054054</v>
@@ -25519,10 +25522,10 @@
         <v>99473.8108108108</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="K9" s="7" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -25533,7 +25536,7 @@
         <v>168</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="E10" s="48" t="n">
         <v>56135.9464864865</v>
@@ -25551,10 +25554,10 @@
         <v>99473.8108108108</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -25562,10 +25565,10 @@
         <v>91</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="E11" s="48" t="n">
         <v>64449.4589189189</v>
@@ -25583,10 +25586,10 @@
         <v>96184.8108108108</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="K11" s="7" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -25594,10 +25597,10 @@
         <v>91</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="E12" s="48" t="n">
         <v>100986.452432432</v>
@@ -25615,10 +25618,10 @@
         <v>96184.8108108108</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="K12" s="7" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -25629,7 +25632,7 @@
         <v>168</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="E13" s="48" t="n">
         <v>67298.1086486487</v>
@@ -25647,10 +25650,10 @@
         <v>96184.8108108108</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="K13" s="7" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -25658,10 +25661,10 @@
         <v>92</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="E14" s="48" t="n">
         <v>66611.6210810811</v>
@@ -25679,10 +25682,10 @@
         <v>110984.810810811</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="K14" s="7" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -25690,10 +25693,10 @@
         <v>92</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="E15" s="48" t="n">
         <v>112108.358918919</v>
@@ -25711,10 +25714,10 @@
         <v>110984.810810811</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -25725,7 +25728,7 @@
         <v>168</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="E16" s="48" t="n">
         <v>68394.5951351351</v>
@@ -25743,15 +25746,15 @@
         <v>110984.810810811</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="K16" s="7" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="3" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
@@ -25768,7 +25771,7 @@
         <v>88</v>
       </c>
       <c r="C19" s="25" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -25776,7 +25779,7 @@
         <v>287</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="D20" s="7"/>
       <c r="E20" s="7"/>
@@ -25789,10 +25792,10 @@
     </row>
     <row r="21" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="7" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="D21" s="7"/>
       <c r="E21" s="7"/>
@@ -25805,10 +25808,10 @@
     </row>
     <row r="22" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="7" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="D22" s="7"/>
       <c r="E22" s="7"/>
@@ -25824,7 +25827,7 @@
         <v>168</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="D23" s="7"/>
       <c r="E23" s="7"/>
@@ -25837,10 +25840,10 @@
     </row>
     <row r="24" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="7" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="D24" s="7"/>
       <c r="E24" s="7"/>
@@ -25853,10 +25856,10 @@
     </row>
     <row r="25" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="7" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="D25" s="7"/>
       <c r="E25" s="7"/>
@@ -25869,10 +25872,10 @@
     </row>
     <row r="26" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="7" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="D26" s="7"/>
       <c r="E26" s="7"/>

--- a/movilizacion/entregables/Simulador_Movilizacion_GRS110.xlsx
+++ b/movilizacion/entregables/Simulador_Movilizacion_GRS110.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Tarifas.xlsx · E7. Se cancela con el WO; ver Pendientes</t>
   </si>
   <si>
-    <t xml:space="preserve">Costo de un pozo en LCI, solo perforación (USD) · SierraCol: 500–600 k</t>
+    <t xml:space="preserve">Costo de un pozo en LCI, solo perforación (USD) · SierraCol: 550–650 k</t>
   </si>
   <si>
     <t xml:space="preserve">Adicionales sobre Lump Sum</t>
@@ -2019,7 +2019,7 @@
     <t xml:space="preserve">Ahorro campaña (USD)</t>
   </si>
   <si>
-    <t xml:space="preserve">% del costo de un pozo (550 k)</t>
+    <t xml:space="preserve">% del costo de un pozo (600 k)</t>
   </si>
   <si>
     <t xml:space="preserve">Horas extra de taladro por movilización que lo anulan</t>
@@ -3445,7 +3445,7 @@
       <c r="L11" s="7"/>
       <c r="M11" s="7"/>
       <c r="N11" s="15" t="n">
-        <v>550000</v>
+        <v>600000</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="M84" s="27" t="n">
         <f aca="false">IF($N$11=0,0,L84/$N$11)</f>
-        <v>0.0078486550789751</v>
+        <v>0.00719460048906051</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4942,7 +4942,7 @@
       </c>
       <c r="M85" s="27" t="n">
         <f aca="false">IF($N$11=0,0,L85/$N$11)</f>
-        <v>-0.0235772316181116</v>
+        <v>-0.0216124623166023</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4979,7 +4979,7 @@
       </c>
       <c r="M86" s="27" t="n">
         <f aca="false">IF($N$11=0,0,L86/$N$11)</f>
-        <v>-0.0235772316181116</v>
+        <v>-0.0216124623166023</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="M87" s="27" t="n">
         <f aca="false">IF($N$11=0,0,L87/$N$11)</f>
-        <v>0.0264651375219375</v>
+        <v>0.0242597093951094</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22206,7 +22206,7 @@
         <v>4316.76029343632</v>
       </c>
       <c r="F18" s="51" t="n">
-        <v>0.00784865507897512</v>
+        <v>0.00719460048906053</v>
       </c>
       <c r="G18" s="52" t="n">
         <v>2.96480789384362</v>
@@ -22238,7 +22238,7 @@
         <v>14555.8256370657</v>
       </c>
       <c r="F19" s="51" t="n">
-        <v>0.0264651375219376</v>
+        <v>0.0242597093951094</v>
       </c>
       <c r="G19" s="52" t="n">
         <v>9.99713299249015</v>
@@ -22270,7 +22270,7 @@
         <v>14979.3966872587</v>
       </c>
       <c r="F20" s="51" t="n">
-        <v>0.0272352667041067</v>
+        <v>0.0249656611454312</v>
       </c>
       <c r="G20" s="52" t="n">
         <v>10.288047175315</v>
@@ -22302,7 +22302,7 @@
         <v>16777.2542857143</v>
       </c>
       <c r="F21" s="51" t="n">
-        <v>0.0305040987012988</v>
+        <v>0.0279620904761905</v>
       </c>
       <c r="G21" s="52" t="n">
         <v>11.5228394819467</v>

--- a/movilizacion/entregables/Simulador_Movilizacion_GRS110.xlsx
+++ b/movilizacion/entregables/Simulador_Movilizacion_GRS110.xlsx
@@ -2387,19 +2387,19 @@
     <t xml:space="preserve">1. FRECUENCIA: AHORRO DE LA CAMPAÑA SEGÚN MOVILIZACIONES POR MES (esperado 5–6)</t>
   </si>
   <si>
-    <t xml:space="preserve">PS normal · horas Excel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lump Sum · horas Excel</t>
+    <t xml:space="preserve">Petro Star tarifa normal · horas Excel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petro Star Lump Sum · horas Excel</t>
   </si>
   <si>
     <t xml:space="preserve">Ecotransur · horas Excel</t>
   </si>
   <si>
-    <t xml:space="preserve">PS normal · horas cotizadas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lump Sum · horas cotizadas</t>
+    <t xml:space="preserve">Petro Star tarifa normal · horas cotizadas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petro Star Lump Sum · horas cotizadas</t>
   </si>
   <si>
     <t xml:space="preserve">Ecotransur · horas cotizadas</t>
@@ -3888,11 +3888,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="12652780"/>
-        <c:axId val="23001895"/>
+        <c:axId val="4302630"/>
+        <c:axId val="60279370"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="12652780"/>
+        <c:axId val="4302630"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3958,7 +3958,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="23001895"/>
+        <c:crossAx val="60279370"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3966,7 +3966,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="23001895"/>
+        <c:axId val="60279370"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4032,7 +4032,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="12652780"/>
+        <c:crossAx val="4302630"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4539,11 +4539,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="8365441"/>
-        <c:axId val="40709801"/>
+        <c:axId val="4867604"/>
+        <c:axId val="48047199"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="8365441"/>
+        <c:axId val="4867604"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4575,7 +4575,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="40709801"/>
+        <c:crossAx val="48047199"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4583,7 +4583,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="40709801"/>
+        <c:axId val="48047199"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4649,7 +4649,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="8365441"/>
+        <c:crossAx val="4867604"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4988,11 +4988,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="22374190"/>
-        <c:axId val="69203286"/>
+        <c:axId val="18037378"/>
+        <c:axId val="89283328"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="22374190"/>
+        <c:axId val="18037378"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5024,7 +5024,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="69203286"/>
+        <c:crossAx val="89283328"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5032,7 +5032,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="69203286"/>
+        <c:axId val="89283328"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5098,7 +5098,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="22374190"/>
+        <c:crossAx val="18037378"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5461,11 +5461,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="84541051"/>
-        <c:axId val="73521582"/>
+        <c:axId val="89715828"/>
+        <c:axId val="65506972"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="84541051"/>
+        <c:axId val="89715828"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5497,7 +5497,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="73521582"/>
+        <c:crossAx val="65506972"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5505,7 +5505,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="73521582"/>
+        <c:axId val="65506972"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5571,7 +5571,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="84541051"/>
+        <c:crossAx val="89715828"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5850,11 +5850,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="76781143"/>
-        <c:axId val="12390632"/>
+        <c:axId val="4454399"/>
+        <c:axId val="23735820"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="76781143"/>
+        <c:axId val="4454399"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5886,7 +5886,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="12390632"/>
+        <c:crossAx val="23735820"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5894,7 +5894,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="12390632"/>
+        <c:axId val="23735820"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5960,7 +5960,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="76781143"/>
+        <c:crossAx val="4454399"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -28516,7 +28516,7 @@
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
     </row>
-    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="5" t="s">
         <v>110</v>
       </c>
